--- a/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:45:49+00:00</t>
+    <t>2026-04-08T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -408,13 +408,14 @@
     <t>fr-lm-entry.header.langue</t>
   </si>
   <si>
-    <t>fr-lm-immunisation.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
+    <t>fr-lm-immunisation.status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Statut de la vaccination (réalisé, non fait, ...).</t>
   </si>
   <si>
     <t>fr-lm-immunisation.periodOfImmunisation</t>
@@ -2473,7 +2474,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2488,13 +2489,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2545,10 +2546,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>

--- a/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-immunisation.xlsx
+++ b/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-immunisation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T10:07:24+00:00</t>
+    <t>2026-04-08T12:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Vaccination</t>
+    <t>EntréeVaccination</t>
   </si>
   <si>
     <t>Purpose</t>
